--- a/results/Int All Data 0.5/Rando_10_permute.xlsx
+++ b/results/Int All Data 0.5/Rando_10_permute.xlsx
@@ -440,1257 +440,1257 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8886061307113939</v>
+        <v>0.8986962598804704</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8882928475033738</v>
+        <v>0.8987396375554271</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8872662425294005</v>
+        <v>0.9037304800462695</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8859914208598419</v>
+        <v>0.9047137073452862</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8859914208598419</v>
+        <v>0.9019592249855408</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8834851551956815</v>
+        <v>0.9019592249855408</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.88444669365722</v>
+        <v>0.9001662810873337</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.88444669365722</v>
+        <v>0.9048655292076344</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8853865432812802</v>
+        <v>0.9003711201079622</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.888854347406979</v>
+        <v>0.9001229034123771</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8867264314632736</v>
+        <v>0.9013760362444574</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8820271833429728</v>
+        <v>0.8957586273375747</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8817139001349528</v>
+        <v>0.8948187777135146</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8817139001349528</v>
+        <v>0.8954453441295547</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8826537497590129</v>
+        <v>0.8962984384037016</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.883593599383073</v>
+        <v>0.8971732215153267</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8839068825910932</v>
+        <v>0.8943536726431462</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8858299595141701</v>
+        <v>0.8918257181415077</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8884229805282436</v>
+        <v>0.9037304800462695</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8902593021014074</v>
+        <v>0.9025641025641025</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8968382494698284</v>
+        <v>0.8931318681318681</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.900662714478504</v>
+        <v>0.8965562945826103</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.900662714478504</v>
+        <v>0.8962430113745903</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.900662714478504</v>
+        <v>0.8888206092153461</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.900662714478504</v>
+        <v>0.8885290148448044</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.9031906689801427</v>
+        <v>0.8882157316367842</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.9091117216117216</v>
+        <v>0.8928716020821283</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9078802776171198</v>
+        <v>0.8916184692500482</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9034075573549258</v>
+        <v>0.8913702525544631</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.9034075573549258</v>
+        <v>0.891056969346443</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.9034075573549258</v>
+        <v>0.8888422980528243</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8967418546365915</v>
+        <v>0.8835381723539618</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8807089839984577</v>
+        <v>0.8885507036822826</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8829019664545981</v>
+        <v>0.8885507036822826</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8695054945054945</v>
+        <v>0.8885507036822826</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8688789280894544</v>
+        <v>0.8847262386736071</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8688789280894544</v>
+        <v>0.8847262386736071</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8720985155195682</v>
+        <v>0.8819066898014267</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8714719491035281</v>
+        <v>0.887654231733179</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.873395026026605</v>
+        <v>0.8905171582803162</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.873395026026605</v>
+        <v>0.890203875072296</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8581501831501832</v>
+        <v>0.8908304414883362</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8581501831501832</v>
+        <v>0.8883241758241758</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8574151725467516</v>
+        <v>0.8857962213225371</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8574151725467516</v>
+        <v>0.8851262772315405</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.873836032388664</v>
+        <v>0.8870493541546174</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8584297281665703</v>
+        <v>0.8899122807017543</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8541738962791594</v>
+        <v>0.8886591478696741</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8349961442066705</v>
+        <v>0.8880205320994794</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8480263157894736</v>
+        <v>0.8861408328513591</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8235444380181223</v>
+        <v>0.8900086755349914</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.822669654906497</v>
+        <v>0.8928499132446501</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8181535569693464</v>
+        <v>0.8951079622132254</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8181535569693464</v>
+        <v>0.8912834972045498</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8181535569693464</v>
+        <v>0.8650520532099479</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8181535569693464</v>
+        <v>0.8653436475804896</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8265591864276074</v>
+        <v>0.8731877771351455</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8243662039714671</v>
+        <v>0.8715779834200887</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8520676691729323</v>
+        <v>0.8750674763832659</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.8491396761133603</v>
+        <v>0.8750674763832659</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.8312054173896279</v>
+        <v>0.8780388471177945</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8308704453441296</v>
+        <v>0.8701730287256603</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.831831983805668</v>
+        <v>0.8685632350106034</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.819645267013688</v>
+        <v>0.8623288991710044</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.8190187005976479</v>
+        <v>0.8581477732793522</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.8154858299595142</v>
+        <v>0.8180981299402352</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.8161340852130325</v>
+        <v>0.8238890495469442</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.8103431656063236</v>
+        <v>0.816218430692115</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7966647387700019</v>
+        <v>0.8302752072488915</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7976045883940621</v>
+        <v>0.8321982841719684</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7625674763832659</v>
+        <v>0.8416835357624832</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.789642375168691</v>
+        <v>0.808408039329092</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7140254482359746</v>
+        <v>0.808408039329092</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7981010217852322</v>
+        <v>0.808408039329092</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7836128783497205</v>
+        <v>0.8071549064970118</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7836128783497205</v>
+        <v>0.8055884904569115</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7829212454212454</v>
+        <v>0.7967081164449585</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.7832562174667438</v>
+        <v>0.7967081164449585</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.7861408328513592</v>
+        <v>0.8172787738577212</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.7861408328513592</v>
+        <v>0.8179053402737613</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.7957562174667437</v>
+        <v>0.8275544630807788</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.7015471370734528</v>
+        <v>0.8272411798727588</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7002940042413727</v>
+        <v>0.8265061692693272</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.698079332947754</v>
+        <v>0.8277809909388857</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.698079332947754</v>
+        <v>0.8175390399074609</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.6979925775978407</v>
+        <v>0.8142543859649123</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.6882036822826296</v>
+        <v>0.817473973395026</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.6553378638904954</v>
+        <v>0.8067235396182764</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.6556511470985155</v>
+        <v>0.815271351455562</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.6248385386543281</v>
+        <v>0.8472720262193947</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.6290630422209369</v>
+        <v>0.8402062849431271</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.6846274339695392</v>
+        <v>0.840519568151147</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.6859022556390977</v>
+        <v>0.827393001735107</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.6537931366878735</v>
+        <v>0.8283545401966455</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.6566777520724889</v>
+        <v>0.8283545401966455</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.6001518218623482</v>
+        <v>0.8213972431077694</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.6001518218623482</v>
+        <v>0.8137049354154617</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.6030364372469635</v>
+        <v>0.7985685367264315</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.6030364372469635</v>
+        <v>0.7995300751879699</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.6177294197031039</v>
+        <v>0.7980624638519376</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.6177294197031039</v>
+        <v>0.8096997300944669</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.6167678812415655</v>
+        <v>0.7603696741854636</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.6219105455947561</v>
+        <v>0.7721346635820321</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.6219105455947561</v>
+        <v>0.7627241179872759</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.636777038750723</v>
+        <v>0.7514989396568343</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.6275086755349913</v>
+        <v>0.7491902834008097</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.6284485251590515</v>
+        <v>0.7411967418546366</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.6236625216888375</v>
+        <v>0.7368541546173125</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.6236625216888375</v>
+        <v>0.7678716020821283</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.6243541546173125</v>
+        <v>0.7696018893387314</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.6599744553691922</v>
+        <v>0.7620830923462503</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.6602877385772122</v>
+        <v>0.7658424908424908</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.66905002891845</v>
+        <v>0.7824272219009061</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5327164064006169</v>
+        <v>0.8000578368999421</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5447079236552921</v>
+        <v>0.8028556969346443</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5592394447657606</v>
+        <v>0.8037955465587044</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5654087140929246</v>
+        <v>0.8053619625988047</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5961683053788317</v>
+        <v>0.8041088297667245</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5844997108155002</v>
+        <v>0.7880783689994216</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5884543088490457</v>
+        <v>0.7192861962598804</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5715779834200887</v>
+        <v>0.7092394447657606</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.6806005398110662</v>
+        <v>0.7127072488914594</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.6806005398110662</v>
+        <v>0.7174064970117602</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.6799522845575477</v>
+        <v>0.7125771158665896</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.6652159244264507</v>
+        <v>0.7259832272990168</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.6938138615770194</v>
+        <v>0.726923076923077</v>
       </c>
     </row>
     <row r="128">
@@ -1700,287 +1700,287 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.6981998264893001</v>
+        <v>0.7159581646423752</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.6902159244264507</v>
+        <v>0.7262097551571236</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.6777159244264508</v>
+        <v>0.729094370541739</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.6806776556776557</v>
+        <v>0.6997228648544438</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.6687728937728938</v>
+        <v>0.6997228648544438</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.6571259880470407</v>
+        <v>0.7115191825718141</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.6577525544630808</v>
+        <v>0.7037738577212261</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.6554945054945055</v>
+        <v>0.7027472527472527</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.6691608829766724</v>
+        <v>0.7027472527472527</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.668199344515134</v>
+        <v>0.7005542702911124</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4808270676691729</v>
+        <v>0.6886928860613071</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5324055330634277</v>
+        <v>0.6724238480817428</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5028243686138423</v>
+        <v>0.7040437632542895</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5012579525737421</v>
+        <v>0.7111842105263158</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5007181415076152</v>
+        <v>0.7221708116444958</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4970021206863312</v>
+        <v>0.7118107769423558</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4999518025833815</v>
+        <v>0.6163895315211105</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5029448621553885</v>
+        <v>0.6216093117408907</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5111384229805283</v>
+        <v>0.6216093117408907</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5111167341430499</v>
+        <v>0.6229058222479276</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5086032388663968</v>
+        <v>0.6280677655677656</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5214695392326971</v>
+        <v>0.6293859649122807</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5195127241179873</v>
+        <v>0.6293859649122807</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5198260073260073</v>
+        <v>0.583157412762676</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.524590321958743</v>
+        <v>0.5460285328706381</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5256169269327164</v>
+        <v>0.5619987468671679</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5256169269327164</v>
+        <v>0.5911099865047234</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5243204164256796</v>
+        <v>0.5940162907268171</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5146592442645074</v>
+        <v>0.5130614999036052</v>
       </c>
     </row>
   </sheetData>
